--- a/final_data_pipeline/output/325312longform.xlsx
+++ b/final_data_pipeline/output/325312longform.xlsx
@@ -819,7 +819,7 @@
         <v>83</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -908,7 +908,7 @@
         <v>83</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -2315,7 +2315,7 @@
         <v>83</v>
       </c>
       <c r="AA18">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB18">
         <v>8000</v>
@@ -2404,7 +2404,7 @@
         <v>83</v>
       </c>
       <c r="AA19">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AB19">
         <v>8000</v>
@@ -4372,7 +4372,7 @@
         <v>83</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4464,7 +4464,7 @@
         <v>83</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4553,7 +4553,7 @@
         <v>83</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4648,7 +4648,7 @@
         <v>83</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4746,7 +4746,7 @@
         <v>83</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4838,7 +4838,7 @@
         <v>83</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4927,7 +4927,7 @@
         <v>83</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -5022,7 +5022,7 @@
         <v>83</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>13.17361111111111</v>
       </c>
       <c r="AB47">
         <v>8000</v>
